--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-11).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-11).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>25</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 8.512,09</t>
+    <t>R$ 8.500,67</t>
   </si>
   <si>
     <t>91.3</t>
   </si>
   <si>
-    <t>62.1</t>
+    <t>61.9</t>
   </si>
   <si>
-    <t>6.06</t>
+    <t>6.08</t>
   </si>
   <si>
-    <t>20.4</t>
+    <t>20.6</t>
   </si>
   <si>
-    <t>7.7</t>
+    <t>7.8</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>33.3%</t>
+    <t>34.0%</t>
   </si>
   <si>
-    <t>18.1%</t>
+    <t>18.0%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -986,19 +986,22 @@
     <t>5.5%</t>
   </si>
   <si>
-    <t>2554.0</t>
+    <t>2557.0</t>
   </si>
   <si>
-    <t>2085.0</t>
+    <t>2088.0</t>
   </si>
   <si>
-    <t>171.0</t>
+    <t>172.0</t>
   </si>
   <si>
     <t>84.0</t>
   </si>
   <si>
-    <t>381.0</t>
+    <t>382.0</t>
+  </si>
+  <si>
+    <t>171.0</t>
   </si>
   <si>
     <t>21.0</t>
@@ -1007,7 +1010,7 @@
     <t>794.0</t>
   </si>
   <si>
-    <t>294.0</t>
+    <t>295.0</t>
   </si>
   <si>
     <t>633.0</t>
@@ -2203,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2233,14 +2236,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>15090.32</v>
+      </c>
+      <c r="N6" s="6">
+        <v>167</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>7.836926347305389</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>17.021144029850745</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.0703007518796994</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.32089552238805968</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4955,7 +4970,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4985,14 +5000,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>10252.17</v>
+      </c>
+      <c r="N24" s="6">
+        <v>111</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>6.0100305555555558</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>22.321072413793104</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.1563218390804604</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.17241379310344829</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6779,7 +6806,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6809,14 +6836,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>7173.8800000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>117</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>10.822968907563025</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>51.698888888888888</v>
+      </c>
+      <c r="R36" s="8">
+        <v>32.33425888888889</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.088888888888888892</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9068,7 +9107,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9098,14 +9137,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1111.8499999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>10</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>6.3200000000000003</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>22.841650000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>11.275</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14770,7 +14821,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14798,14 +14849,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>9964.6599999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>91</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>6.7153699999999992</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>22.97483725490196</v>
+      </c>
+      <c r="R89" s="8">
+        <v>8.7770833333333336</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.15686274509803921</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -18012,7 +18075,9 @@
       <c r="N111" s="6">
         <v>31</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>28</v>
+      </c>
       <c r="P111" s="7">
         <v>5.7927093750000003</v>
       </c>
@@ -18022,31 +18087,75 @@
       <c r="R111" s="8">
         <v>1.2529749999999999</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.7142857142857143</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -25057,7 +25166,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25087,14 +25196,26 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
+      <c r="M158" s="5">
+        <v>5276.8999999999996</v>
+      </c>
+      <c r="N158" s="6">
+        <v>47</v>
+      </c>
       <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
+      <c r="P158" s="7">
+        <v>2.392156862745098</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>12.659090909090908</v>
+      </c>
+      <c r="R158" s="8">
+        <v>3.2151515151515149</v>
+      </c>
       <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
+      <c r="T158" s="9">
+        <v>1.0303030303030303</v>
+      </c>
       <c r="U158" s="9"/>
       <c r="V158" s="9"/>
       <c r="W158" s="9"/>
@@ -28268,7 +28389,9 @@
       <c r="N179" s="6">
         <v>86</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>43</v>
+      </c>
       <c r="P179" s="7">
         <v>3.0801583333333333</v>
       </c>
@@ -28278,31 +28401,75 @@
       <c r="R179" s="8">
         <v>1.4542627906976744</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.97674418604651159</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -33546,25 +33713,25 @@
         <v>329</v>
       </c>
       <c t="s" r="AI216" s="11">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="AJ216" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AK216" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AL216" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AM216" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33581,10 +33748,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
